--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2024_los_rios_sexo.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2024_los_rios_sexo.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:10</t>
+    <t xml:space="preserve">2026-10-05 06:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
